--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440494</v>
       </c>
       <c r="B2" t="n">
-        <v>91290</v>
+        <v>91306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440494</v>
       </c>
       <c r="B2" t="n">
-        <v>91306</v>
+        <v>91318</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440494</v>
       </c>
       <c r="B2" t="n">
-        <v>91318</v>
+        <v>91340</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440494</v>
       </c>
       <c r="B2" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440494</v>
       </c>
       <c r="B2" t="n">
-        <v>91344</v>
+        <v>91350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440494</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>91357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440494</v>
       </c>
       <c r="B2" t="n">
-        <v>91357</v>
+        <v>91362</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440494</v>
       </c>
       <c r="B2" t="n">
-        <v>91362</v>
+        <v>91390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440494</v>
       </c>
       <c r="B2" t="n">
-        <v>91390</v>
+        <v>91394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,312 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125007035</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>749434</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7193642</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125006471</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78842</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>749395</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7193694</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125007036</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>749405</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7193668</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125006471</v>
+        <v>125007036</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749395</v>
+        <v>749405</v>
       </c>
       <c r="R4" t="n">
-        <v>7193694</v>
+        <v>7193668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007036</v>
+        <v>125006471</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749405</v>
+        <v>749395</v>
       </c>
       <c r="R5" t="n">
-        <v>7193668</v>
+        <v>7193694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007035</v>
+        <v>125007036</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749434</v>
+        <v>749405</v>
       </c>
       <c r="R3" t="n">
-        <v>7193642</v>
+        <v>7193668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007036</v>
+        <v>125006471</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749405</v>
+        <v>749395</v>
       </c>
       <c r="R4" t="n">
-        <v>7193668</v>
+        <v>7193694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125006471</v>
+        <v>125007035</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749395</v>
+        <v>749434</v>
       </c>
       <c r="R5" t="n">
-        <v>7193694</v>
+        <v>7193642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125006471</v>
+        <v>125007035</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749395</v>
+        <v>749434</v>
       </c>
       <c r="R4" t="n">
-        <v>7193694</v>
+        <v>7193642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007035</v>
+        <v>125006471</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749434</v>
+        <v>749395</v>
       </c>
       <c r="R5" t="n">
-        <v>7193642</v>
+        <v>7193694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007036</v>
+        <v>125006471</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749405</v>
+        <v>749395</v>
       </c>
       <c r="R3" t="n">
-        <v>7193668</v>
+        <v>7193694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007035</v>
+        <v>125007036</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749434</v>
+        <v>749405</v>
       </c>
       <c r="R4" t="n">
-        <v>7193642</v>
+        <v>7193668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125006471</v>
+        <v>125007035</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749395</v>
+        <v>749434</v>
       </c>
       <c r="R5" t="n">
-        <v>7193694</v>
+        <v>7193642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125006471</v>
+        <v>125007036</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749395</v>
+        <v>749405</v>
       </c>
       <c r="R3" t="n">
-        <v>7193694</v>
+        <v>7193668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007036</v>
+        <v>125007035</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749405</v>
+        <v>749434</v>
       </c>
       <c r="R4" t="n">
-        <v>7193668</v>
+        <v>7193642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007035</v>
+        <v>125006471</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749434</v>
+        <v>749395</v>
       </c>
       <c r="R5" t="n">
-        <v>7193642</v>
+        <v>7193694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125006471</v>
+        <v>125007036</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749395</v>
+        <v>749405</v>
       </c>
       <c r="R3" t="n">
-        <v>7193694</v>
+        <v>7193668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007036</v>
+        <v>125006471</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749405</v>
+        <v>749395</v>
       </c>
       <c r="R4" t="n">
-        <v>7193668</v>
+        <v>7193694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007036</v>
+        <v>125007035</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749405</v>
+        <v>749434</v>
       </c>
       <c r="R3" t="n">
-        <v>7193668</v>
+        <v>7193642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125006471</v>
+        <v>125007036</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749395</v>
+        <v>749405</v>
       </c>
       <c r="R4" t="n">
-        <v>7193694</v>
+        <v>7193668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007035</v>
+        <v>125006471</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749434</v>
+        <v>749395</v>
       </c>
       <c r="R5" t="n">
-        <v>7193642</v>
+        <v>7193694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007035</v>
+        <v>125007036</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749434</v>
+        <v>749405</v>
       </c>
       <c r="R3" t="n">
-        <v>7193642</v>
+        <v>7193668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007036</v>
+        <v>125007035</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749405</v>
+        <v>749434</v>
       </c>
       <c r="R4" t="n">
-        <v>7193668</v>
+        <v>7193642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007036</v>
+        <v>125006471</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749405</v>
+        <v>749395</v>
       </c>
       <c r="R3" t="n">
-        <v>7193668</v>
+        <v>7193694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007035</v>
+        <v>125007036</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749434</v>
+        <v>749405</v>
       </c>
       <c r="R4" t="n">
-        <v>7193642</v>
+        <v>7193668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125006471</v>
+        <v>125007035</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749395</v>
+        <v>749434</v>
       </c>
       <c r="R5" t="n">
-        <v>7193694</v>
+        <v>7193642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125006471</v>
+        <v>125007035</v>
       </c>
       <c r="B3" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749395</v>
+        <v>749434</v>
       </c>
       <c r="R3" t="n">
-        <v>7193694</v>
+        <v>7193642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007035</v>
+        <v>125006471</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749434</v>
+        <v>749395</v>
       </c>
       <c r="R5" t="n">
-        <v>7193642</v>
+        <v>7193694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 70868-2021 artfynd.xlsx
+++ b/artfynd/A 70868-2021 artfynd.xlsx
@@ -782,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007035</v>
+        <v>125006471</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749434</v>
+        <v>749395</v>
       </c>
       <c r="R3" t="n">
-        <v>7193642</v>
+        <v>7193694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,16 +879,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007036</v>
+        <v>125007035</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>NT</t>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749405</v>
+        <v>749434</v>
       </c>
       <c r="R4" t="n">
-        <v>7193668</v>
+        <v>7193642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125006471</v>
+        <v>125007036</v>
       </c>
       <c r="B5" t="n">
-        <v>78979</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749395</v>
+        <v>749405</v>
       </c>
       <c r="R5" t="n">
-        <v>7193694</v>
+        <v>7193668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
